--- a/StructureDefinition-ophthalmic-diagnostic-report.xlsx
+++ b/StructureDefinition-ophthalmic-diagnostic-report.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-diagnostic-report.xlsx
+++ b/StructureDefinition-ophthalmic-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -608,8 +608,8 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
-    <t>value:coding.code}
-value:coding.system}</t>
+    <t xml:space="preserve">pattern:$this}
+</t>
   </si>
   <si>
     <t>open</t>
@@ -1432,17 +1432,17 @@
   <dimension ref="A1:AN35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.6171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.6171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.36328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.36328125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="54.296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.25390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="77.734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1451,26 +1451,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="41.5390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.3515625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="41.98046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.59765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="147.17578125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="104.53515625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="148.8984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="105.9453125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.45703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-ophthalmic-diagnostic-report.xlsx
+++ b/StructureDefinition-ophthalmic-diagnostic-report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="343">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:17:00-03:00</t>
+    <t>2026-10-20T20:13:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,10 +87,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Represents the findings, diagnosis, and treatment plan reached after
-reviewing an imaging study or structured examination dataset. Unlike a radiology report,
-this is not limited to describing imaging findings: the same clinical act typically also
-reaches a diagnosis and defines a treatment plan, recorded as separate Condition and
+    <t>Represents the findings, diagnosis, and treatment plan reached after
+reviewing an imaging study or structured examination dataset. Unlike a radiology report,
+this is not limited to describing imaging findings: the same clinical act typically also
+reaches a diagnosis and defines a treatment plan, recorded as separate Condition and
 CarePlan resources referencing this report.</t>
   </si>
   <si>
@@ -648,10 +648,13 @@
     <t>IMG (Diagnostic Imaging), only when the exam is image-based; omitted otherwise</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0074</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0074"/&gt;
+    &lt;code value="IMG"/&gt;
+    &lt;display value="Diagnostic Imaging"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -3245,7 +3248,7 @@
         <v>81</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>81</v>
@@ -3260,11 +3263,13 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -3311,14 +3316,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3340,10 +3345,10 @@
         <v>181</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3373,11 +3378,11 @@
         <v>115</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
       </c>
@@ -3394,7 +3399,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>91</v>
@@ -3409,28 +3414,28 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3449,17 +3454,17 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -3508,7 +3513,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3523,28 +3528,28 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3563,19 +3568,19 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -3624,7 +3629,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3639,28 +3644,28 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3679,19 +3684,19 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -3740,7 +3745,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3755,28 +3760,28 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>242</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3795,19 +3800,19 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -3856,7 +3861,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3874,25 +3879,25 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3911,19 +3916,19 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -3972,7 +3977,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3987,28 +3992,28 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4027,19 +4032,19 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="N23" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="O23" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4088,7 +4093,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4103,24 +4108,24 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4143,19 +4148,19 @@
         <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4204,7 +4209,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4222,10 +4227,10 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4233,14 +4238,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4259,19 +4264,19 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4320,7 +4325,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4338,10 +4343,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4349,10 +4354,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4375,16 +4380,16 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4434,7 +4439,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4455,7 +4460,7 @@
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -4463,14 +4468,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4489,17 +4494,17 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -4548,7 +4553,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4566,10 +4571,10 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -4577,10 +4582,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4603,13 +4608,13 @@
         <v>81</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4660,7 +4665,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4681,7 +4686,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -4689,10 +4694,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4721,7 +4726,7 @@
         <v>138</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>140</v>
@@ -4774,7 +4779,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4795,7 +4800,7 @@
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -4803,14 +4808,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4832,10 +4837,10 @@
         <v>137</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>140</v>
@@ -4890,7 +4895,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4919,10 +4924,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4945,19 +4950,19 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5006,7 +5011,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5027,7 +5032,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5035,10 +5040,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5061,13 +5066,13 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5118,7 +5123,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>91</v>
@@ -5139,7 +5144,7 @@
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5147,14 +5152,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5173,17 +5178,17 @@
         <v>81</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -5232,7 +5237,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5250,10 +5255,10 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5261,10 +5266,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5290,10 +5295,10 @@
         <v>181</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5323,11 +5328,11 @@
         <v>185</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>81</v>
       </c>
@@ -5344,7 +5349,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5362,10 +5367,10 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5373,10 +5378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5399,19 +5404,19 @@
         <v>81</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5460,7 +5465,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5478,10 +5483,10 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
